--- a/组合实盘追踪/20260515_银河.xlsx
+++ b/组合实盘追踪/20260515_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>702.4</v>
+        <v>708.4</v>
       </c>
       <c r="D2" s="1">
-        <v>-3.4</v>
+        <v>2.6</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0048</v>
+        <v>0.0037</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,16 +553,16 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="L2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="N2" s="1">
         <v>-9.9</v>
@@ -574,7 +574,7 @@
         <v>-9.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>5</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0048</v>
+        <v>0.0037</v>
       </c>
       <c r="U2" s="5">
-        <v>3.512</v>
+        <v>3.542</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0125</v>
+        <v>0.004</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0763</v>
+        <v>0.0855</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0691</v>
+        <v>0.0783</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1715</v>
+        <v>0.1815</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4407</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>844</v>
+        <v>841.6</v>
       </c>
       <c r="D3" s="1">
-        <v>-13.6</v>
+        <v>-16</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0159</v>
+        <v>-0.0187</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
+        <v>-21.3</v>
+      </c>
+      <c r="K3" s="2">
+        <v>-0.0247</v>
+      </c>
+      <c r="L3" s="1">
+        <v>-21.3</v>
+      </c>
+      <c r="M3" s="2">
+        <v>-0.0247</v>
+      </c>
+      <c r="N3" s="1">
         <v>-18.9</v>
       </c>
-      <c r="K3" s="2">
-        <v>-0.0219</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="O3" s="1">
         <v>-18.9</v>
       </c>
-      <c r="M3" s="2">
-        <v>-0.0219</v>
-      </c>
-      <c r="N3" s="1">
-        <v>-18.5</v>
-      </c>
-      <c r="O3" s="1">
-        <v>-18.5</v>
-      </c>
       <c r="P3" s="1">
-        <v>-18.5</v>
+        <v>-18.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0287</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>5</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0159</v>
+        <v>-0.0187</v>
       </c>
       <c r="U3" s="5">
-        <v>2.11</v>
+        <v>2.104</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0223</v>
+        <v>0.0252</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0005</v>
+        <v>-0.0033</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0561</v>
+        <v>0.0531</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1024</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>720.5</v>
+        <v>722.7</v>
       </c>
       <c r="D4" s="1">
-        <v>-13.2</v>
+        <v>-11</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,16 +719,16 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-16.6</v>
+        <v>-14.4</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0225</v>
+        <v>-0.0195</v>
       </c>
       <c r="L4" s="1">
-        <v>-16.6</v>
+        <v>-14.4</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0225</v>
+        <v>-0.0195</v>
       </c>
       <c r="N4" s="1">
         <v>-16.6</v>
@@ -749,28 +749,28 @@
         <v>5</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="U4" s="5">
-        <v>0.655</v>
+        <v>0.657</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0229</v>
+        <v>0.0198</v>
       </c>
       <c r="X4" s="2">
-        <v>0.025</v>
+        <v>0.0282</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0941</v>
+        <v>-0.0913</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1863</v>
+        <v>-0.1838</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1232</v>
+        <v>-0.1205</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>980.4</v>
+        <v>986.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-7.8</v>
+        <v>-1.6</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0079</v>
+        <v>-0.0016</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,16 +802,16 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-10.9</v>
+        <v>-4.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.011</v>
+        <v>-0.0047</v>
       </c>
       <c r="L5" s="1">
-        <v>-10.9</v>
+        <v>-4.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.011</v>
+        <v>-0.0047</v>
       </c>
       <c r="N5" s="1">
         <v>-11.9</v>
@@ -823,7 +823,7 @@
         <v>-11.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>5</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0079</v>
+        <v>-0.0016</v>
       </c>
       <c r="U5" s="5">
-        <v>4.902</v>
+        <v>4.933</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0112</v>
+        <v>0.0049</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0403</v>
+        <v>0.0469</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0495</v>
+        <v>0.0561</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0609</v>
+        <v>0.0676</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2715</v>
+        <v>0.2795</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>964.4</v>
+        <v>963.8</v>
       </c>
       <c r="D6" s="1">
-        <v>-15.1</v>
+        <v>-15.7</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0154</v>
+        <v>-0.016</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-9.3</v>
+        <v>-9.9</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0096</v>
+        <v>-0.0102</v>
       </c>
       <c r="L6" s="1">
-        <v>-9.3</v>
+        <v>-9.9</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0096</v>
+        <v>-0.0102</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="O6" s="1">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="P6" s="1">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0328</v>
+        <v>0.0326</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>5</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0154</v>
+        <v>-0.016</v>
       </c>
       <c r="U6" s="5">
-        <v>9.644</v>
+        <v>9.638</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0096</v>
+        <v>0.0103</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0367</v>
+        <v>-0.0373</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0881</v>
+        <v>-0.0886</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0602</v>
+        <v>0.0595</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3253</v>
+        <v>0.3244</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1026</v>
+        <v>0.1022</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>786.4</v>
+        <v>796.6</v>
       </c>
       <c r="D8" s="1">
-        <v>-5.8</v>
+        <v>4.4</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0073</v>
+        <v>0.0056</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-0.3</v>
+        <v>9.9</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0004</v>
+        <v>0.0126</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.3</v>
+        <v>9.9</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0004</v>
+        <v>0.0126</v>
       </c>
       <c r="N8" s="1">
-        <v>0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="O8" s="1">
-        <v>0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="P8" s="1">
-        <v>0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0267</v>
+        <v>0.027</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>5</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0073</v>
+        <v>0.0056</v>
       </c>
       <c r="U8" s="5">
-        <v>3.932</v>
+        <v>3.983</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0005</v>
+        <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1076</v>
+        <v>0.122</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2043</v>
+        <v>0.2199</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2712</v>
+        <v>0.2877</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9143</v>
+        <v>0.9391</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19878.6</v>
+        <v>19966.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-44.8</v>
+        <v>43.4</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0022</v>
+        <v>0.0022</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-499.04</v>
+        <v>-410.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0245</v>
+        <v>-0.0202</v>
       </c>
       <c r="L9" s="1">
-        <v>-499.04</v>
+        <v>-410.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0245</v>
+        <v>-0.0202</v>
       </c>
       <c r="N9" s="1">
-        <v>-504.64</v>
+        <v>-515.84</v>
       </c>
       <c r="O9" s="1">
-        <v>-504.64</v>
+        <v>-515.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-504.64</v>
+        <v>-515.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6754</v>
+        <v>0.6759</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>5</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0022</v>
+        <v>0.0022</v>
       </c>
       <c r="U9" s="5">
-        <v>14.199</v>
+        <v>14.262</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0251</v>
+        <v>0.0205</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0084</v>
+        <v>0.0129</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0287</v>
+        <v>-0.0244</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0386</v>
+        <v>0.0432</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1813</v>
+        <v>0.1866</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>663.6</v>
+        <v>660.4</v>
       </c>
       <c r="D10" s="1">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0197</v>
+        <v>0.0148</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-8.5</v>
+        <v>-11.7</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0126</v>
+        <v>-0.0174</v>
       </c>
       <c r="L10" s="1">
-        <v>-8.5</v>
+        <v>-11.7</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0126</v>
+        <v>-0.0174</v>
       </c>
       <c r="N10" s="1">
         <v>-8.5</v>
@@ -1238,7 +1238,7 @@
         <v>-8.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>5</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0197</v>
+        <v>0.0148</v>
       </c>
       <c r="U10" s="5">
-        <v>1.659</v>
+        <v>1.651</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0127</v>
+        <v>0.0176</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0215</v>
+        <v>0.0166</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.3073</v>
+        <v>0.301</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3621</v>
+        <v>0.3555</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2298</v>
+        <v>0.2239</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>865.2</v>
+        <v>865.6</v>
       </c>
       <c r="D11" s="1">
-        <v>-6.4</v>
+        <v>-6</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0073</v>
+        <v>-0.0069</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0055</v>
+        <v>0.0059</v>
       </c>
       <c r="L11" s="1">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0055</v>
+        <v>0.0059</v>
       </c>
       <c r="N11" s="1">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="O11" s="1">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="P11" s="1">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0294</v>
+        <v>0.0293</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>5</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0073</v>
+        <v>-0.0069</v>
       </c>
       <c r="U11" s="5">
-        <v>2.163</v>
+        <v>2.164</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0369</v>
+        <v>0.0374</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0541</v>
+        <v>0.0546</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1918</v>
+        <v>0.1923</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2783</v>
+        <v>0.2789</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29424.1</v>
+        <v>29531.1</v>
       </c>
       <c r="D12" s="1">
-        <v>-97.3</v>
+        <v>9.7</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0033</v>
+        <v>0.0003</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-567.69</v>
+        <v>-460.69</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0189</v>
+        <v>-0.0154</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-574.99</v>
+        <v>-590.09</v>
       </c>
       <c r="O12" s="1">
-        <v>-574.99</v>
+        <v>-590.09</v>
       </c>
       <c r="P12" s="1">
-        <v>-574.99</v>
+        <v>-590.09</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/组合实盘追踪/20260515_银河.xlsx
+++ b/组合实盘追踪/20260515_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>708.4</v>
+        <v>697.6</v>
       </c>
       <c r="D2" s="1">
-        <v>2.6</v>
+        <v>-8.2</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0037</v>
+        <v>-0.0116</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,16 +553,16 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-2.7</v>
+        <v>-13.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0038</v>
+        <v>-0.019</v>
       </c>
       <c r="L2" s="1">
-        <v>-2.7</v>
+        <v>-13.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0038</v>
+        <v>-0.019</v>
       </c>
       <c r="N2" s="1">
         <v>-9.9</v>
@@ -574,7 +574,7 @@
         <v>-9.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.024</v>
+        <v>0.0238</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>5</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0037</v>
+        <v>-0.0116</v>
       </c>
       <c r="U2" s="5">
-        <v>3.542</v>
+        <v>3.488</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.004</v>
+        <v>0.0195</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0855</v>
+        <v>0.0689</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0783</v>
+        <v>0.0618</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1815</v>
+        <v>0.1635</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.453</v>
+        <v>0.4309</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>841.6</v>
+        <v>835.6</v>
       </c>
       <c r="D3" s="1">
-        <v>-16</v>
+        <v>-22</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0187</v>
+        <v>-0.0257</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-21.3</v>
+        <v>-27.3</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0247</v>
+        <v>-0.0316</v>
       </c>
       <c r="L3" s="1">
-        <v>-21.3</v>
+        <v>-27.3</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0247</v>
+        <v>-0.0316</v>
       </c>
       <c r="N3" s="1">
         <v>-18.9</v>
@@ -666,28 +666,28 @@
         <v>5</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0187</v>
+        <v>-0.0257</v>
       </c>
       <c r="U3" s="5">
-        <v>2.104</v>
+        <v>2.089</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0252</v>
+        <v>0.0326</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0033</v>
+        <v>-0.0105</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.052</v>
+        <v>0.0445</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0531</v>
+        <v>0.0456</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0993</v>
+        <v>0.0915</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>722.7</v>
+        <v>713.9</v>
       </c>
       <c r="D4" s="1">
-        <v>-11</v>
+        <v>-19.8</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.015</v>
+        <v>-0.027</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,16 +719,16 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-14.4</v>
+        <v>-23.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0195</v>
+        <v>-0.0315</v>
       </c>
       <c r="L4" s="1">
-        <v>-14.4</v>
+        <v>-23.2</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0195</v>
+        <v>-0.0315</v>
       </c>
       <c r="N4" s="1">
         <v>-16.6</v>
@@ -740,7 +740,7 @@
         <v>-16.6</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0245</v>
+        <v>0.0244</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>5</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.015</v>
+        <v>-0.027</v>
       </c>
       <c r="U4" s="5">
-        <v>0.657</v>
+        <v>0.649</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0198</v>
+        <v>0.0324</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0282</v>
+        <v>0.0156</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0913</v>
+        <v>-0.1024</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1838</v>
+        <v>-0.1938</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1205</v>
+        <v>-0.1312</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>986.6</v>
+        <v>975.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-1.6</v>
+        <v>-12.6</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0016</v>
+        <v>-0.0128</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,16 +802,16 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-4.7</v>
+        <v>-15.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0158</v>
       </c>
       <c r="L5" s="1">
-        <v>-4.7</v>
+        <v>-15.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0158</v>
       </c>
       <c r="N5" s="1">
         <v>-11.9</v>
@@ -823,7 +823,7 @@
         <v>-11.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0334</v>
+        <v>0.0333</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>5</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0016</v>
+        <v>-0.0128</v>
       </c>
       <c r="U5" s="5">
-        <v>4.933</v>
+        <v>4.878</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0049</v>
+        <v>0.0162</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0469</v>
+        <v>0.0352</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0561</v>
+        <v>0.0443</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0676</v>
+        <v>0.0557</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2795</v>
+        <v>0.2653</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>963.8</v>
+        <v>955.4</v>
       </c>
       <c r="D6" s="1">
-        <v>-15.7</v>
+        <v>-24.1</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.016</v>
+        <v>-0.0246</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,16 +885,16 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-9.9</v>
+        <v>-18.3</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0102</v>
+        <v>-0.0188</v>
       </c>
       <c r="L6" s="1">
-        <v>-9.9</v>
+        <v>-18.3</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0102</v>
+        <v>-0.0188</v>
       </c>
       <c r="N6" s="1">
         <v>-9.9</v>
@@ -915,28 +915,28 @@
         <v>5</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.016</v>
+        <v>-0.0246</v>
       </c>
       <c r="U6" s="5">
-        <v>9.638</v>
+        <v>9.554</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0103</v>
+        <v>0.0192</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0373</v>
+        <v>-0.0457</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0886</v>
+        <v>-0.0966</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0595</v>
+        <v>0.0503</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3244</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3018.6</v>
+        <v>3021.3</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,16 +968,16 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>-0.15</v>
+        <v>2.55</v>
       </c>
       <c r="K7" s="2">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.15</v>
+        <v>2.55</v>
       </c>
       <c r="M7" s="2">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="N7" s="1">
         <v>-0.15</v>
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1022</v>
+        <v>0.1032</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>5</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.118</v>
+        <v>1.119</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0072</v>
+        <v>0.0081</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0118</v>
+        <v>0.0127</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0188</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>796.6</v>
+        <v>794</v>
       </c>
       <c r="D8" s="1">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0056</v>
+        <v>0.0023</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,16 +1051,16 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0126</v>
+        <v>0.0093</v>
       </c>
       <c r="L8" s="1">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0126</v>
+        <v>0.0093</v>
       </c>
       <c r="N8" s="1">
         <v>-1.9</v>
@@ -1072,7 +1072,7 @@
         <v>-1.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.027</v>
+        <v>0.0271</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>5</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0056</v>
+        <v>0.0023</v>
       </c>
       <c r="U8" s="5">
-        <v>3.983</v>
+        <v>3.97</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.122</v>
+        <v>0.1183</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2199</v>
+        <v>0.216</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2877</v>
+        <v>0.2835</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9391</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19966.8</v>
+        <v>19768</v>
       </c>
       <c r="D9" s="1">
-        <v>43.4</v>
+        <v>-155.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,16 +1134,16 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-410.84</v>
+        <v>-609.64</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0202</v>
+        <v>-0.0299</v>
       </c>
       <c r="L9" s="1">
-        <v>-410.84</v>
+        <v>-609.64</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0202</v>
+        <v>-0.0299</v>
       </c>
       <c r="N9" s="1">
         <v>-515.84</v>
@@ -1155,7 +1155,7 @@
         <v>-515.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6759</v>
+        <v>0.6751</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>5</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="U9" s="5">
-        <v>14.262</v>
+        <v>14.12</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0205</v>
+        <v>0.0308</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0129</v>
+        <v>0.0028</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0244</v>
+        <v>-0.0341</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0432</v>
+        <v>0.0328</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1866</v>
+        <v>0.1748</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>660.4</v>
+        <v>659.6</v>
       </c>
       <c r="D10" s="1">
-        <v>9.6</v>
+        <v>8.8</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0148</v>
+        <v>0.0135</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-11.7</v>
+        <v>-12.5</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0174</v>
+        <v>-0.0186</v>
       </c>
       <c r="L10" s="1">
-        <v>-11.7</v>
+        <v>-12.5</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0174</v>
+        <v>-0.0186</v>
       </c>
       <c r="N10" s="1">
         <v>-8.5</v>
@@ -1238,7 +1238,7 @@
         <v>-8.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0224</v>
+        <v>0.0225</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>5</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0148</v>
+        <v>0.0135</v>
       </c>
       <c r="U10" s="5">
-        <v>1.651</v>
+        <v>1.649</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0176</v>
+        <v>0.0188</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0166</v>
+        <v>0.0153</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.301</v>
+        <v>0.2994</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3555</v>
+        <v>0.3539</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2239</v>
+        <v>0.2224</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>865.6</v>
+        <v>852.4</v>
       </c>
       <c r="D11" s="1">
-        <v>-6</v>
+        <v>-19.2</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0069</v>
+        <v>-0.022</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,16 +1300,16 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>5.1</v>
+        <v>-8.1</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0059</v>
+        <v>-0.0094</v>
       </c>
       <c r="L11" s="1">
-        <v>5.1</v>
+        <v>-8.1</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0059</v>
+        <v>-0.0094</v>
       </c>
       <c r="N11" s="1">
         <v>3.5</v>
@@ -1321,7 +1321,7 @@
         <v>3.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0293</v>
+        <v>0.0291</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>5</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0069</v>
+        <v>-0.022</v>
       </c>
       <c r="U11" s="5">
-        <v>2.164</v>
+        <v>2.131</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v/>
+        <v>0.0094</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0374</v>
+        <v>0.0216</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0546</v>
+        <v>0.0385</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1923</v>
+        <v>0.1742</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2789</v>
+        <v>0.2594</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29531.1</v>
+        <v>29273.4</v>
       </c>
       <c r="D12" s="1">
-        <v>9.7</v>
+        <v>-248</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0003</v>
+        <v>-0.0084</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-460.69</v>
+        <v>-718.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0154</v>
+        <v>-0.024</v>
       </c>
       <c r="L12" t="str">
         <v/>
